--- a/human_resources_surveys/016_corporate_internal_communication_effectiveness_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/016_corporate_internal_communication_effectiveness_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,23 +515,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_1</t>
+          <t>communication_effectiveness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Communication Effectiveness</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>How would you rate the overall effectiveness of internal communication in the company?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Rate the effectiveness of internal communication</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,18 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_2</t>
+          <t>frequency_of_feedback</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Frequency of Communication</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>How often do you receive feedback from your supervisor?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Rate the frequency of feedback you receive</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_3</t>
+          <t>channels_used</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Communication Channels</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Which of the following channels do you most frequently use to receive company information?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Select the channel you most frequently use</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_4</t>
+          <t>communication_style</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Communication Style</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>How would you rate the communication style of the company's management?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Rate the transparency of company management</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,110 +628,211 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_5</t>
+          <t>types_of_info</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Communication Effectiveness</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Which of the following types of information do you most frequently receive from the company?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Select the type of information you most frequently receive</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_6</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Information Flow</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>How would you rate your overall satisfaction with internal communication in the company?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Rate your overall satisfaction</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_7</t>
+          <t>questions_concerns</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Frequency of Communication</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>How often do you feel that your questions and concerns are addressed by the company?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rate the frequency of questions and concerns addressed</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_8</t>
+          <t>timeliness_of_info</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Communication Channels</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
+          <t>How would you rate the timeliness of information provided by the company?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Rate the timeliness of company information</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>channels_used_for_feedback</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Which of the following channels do you most frequently use to ask questions or provide feedback to the company?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select the channel you most frequently use</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>select_one</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_9</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Communication Style</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>clarity_of_info</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>How would you rate the clarity of information provided by the company?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Rate the clarity of company information</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Do you have any additional comments or suggestions regarding internal communication in the company?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Provide any additional comments or suggestions</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>other_comments</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Any other comments or suggestions for the company?</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Provide any other comments or suggestions</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -730,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -758,306 +875,799 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_1_choices</t>
+          <t>communication_effectiveness_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_1_choices</t>
+          <t>communication_effectiveness_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_2_choices</t>
+          <t>communication_effectiveness_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_2_choices</t>
+          <t>communication_effectiveness_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_3_choices</t>
+          <t>frequency_of_feedback_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_3_choices</t>
+          <t>frequency_of_feedback_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_4_choices</t>
+          <t>frequency_of_feedback_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_4_choices</t>
+          <t>frequency_of_feedback_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_5_choices</t>
+          <t>channels_used_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_5_choices</t>
+          <t>channels_used_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_6_choices</t>
+          <t>channels_used_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_6_choices</t>
+          <t>channels_used_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_7_choices</t>
+          <t>channels_used_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_7_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_8_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_8_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_9_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>corporate_internal_communication_effectiveness_survey_page_9_choices</t>
+          <t>communication_style_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Option 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>types_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>types_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>types_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>types_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>types_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>option_5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Option 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>option_5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Option 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>questions_concerns_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>questions_concerns_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>questions_concerns_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>questions_concerns_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>timeliness_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>timeliness_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>timeliness_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>timeliness_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>timeliness_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>option_5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Option 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>channels_used_for_feedback_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>channels_used_for_feedback_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>channels_used_for_feedback_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>channels_used_for_feedback_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>channels_used_for_feedback_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>option_5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Option 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>clarity_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>option_1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Option 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>clarity_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>option_2</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Option 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>clarity_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>option_3</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Option 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>clarity_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>option_4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Option 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>clarity_of_info_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>option_5</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
